--- a/assets/files/tabel_nilai_10_siswa.xlsx
+++ b/assets/files/tabel_nilai_10_siswa.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\laragon\www\kursus\assets\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77A06923-06C9-4FFE-A008-922A4C09D524}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF503D4A-1FD0-4B2F-963D-D9F6E3831921}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" xr2:uid="{88E769A1-D518-416B-BC97-DFCCD6443C9C}"/>
+    <workbookView xWindow="-20610" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{88E769A1-D518-416B-BC97-DFCCD6443C9C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -48,36 +48,6 @@
     <t>KETERANGAN</t>
   </si>
   <si>
-    <t>Andi </t>
-  </si>
-  <si>
-    <t>Budi </t>
-  </si>
-  <si>
-    <t>Cici </t>
-  </si>
-  <si>
-    <t>Dodi </t>
-  </si>
-  <si>
-    <t>Eka </t>
-  </si>
-  <si>
-    <t>Fani </t>
-  </si>
-  <si>
-    <t>Gita </t>
-  </si>
-  <si>
-    <t>Hadi </t>
-  </si>
-  <si>
-    <t>Indah </t>
-  </si>
-  <si>
-    <t>Joko </t>
-  </si>
-  <si>
     <t>LULUS</t>
   </si>
   <si>
@@ -85,6 +55,36 @@
   </si>
   <si>
     <t>TABEL DATA NILAI SISWA</t>
+  </si>
+  <si>
+    <t>Andi</t>
+  </si>
+  <si>
+    <t>Budi</t>
+  </si>
+  <si>
+    <t>Cici</t>
+  </si>
+  <si>
+    <t>Dodi</t>
+  </si>
+  <si>
+    <t>Eka</t>
+  </si>
+  <si>
+    <t>Fani</t>
+  </si>
+  <si>
+    <t>Gita</t>
+  </si>
+  <si>
+    <t>Hadi</t>
+  </si>
+  <si>
+    <t>Indah</t>
+  </si>
+  <si>
+    <t>Joko</t>
   </si>
 </sst>
 </file>
@@ -211,9 +211,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -251,7 +251,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -357,7 +357,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -499,7 +499,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -515,15 +515,15 @@
     <col min="5" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
       <c r="D1" s="8"/>
     </row>
-    <row r="2" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>0</v>
       </c>
@@ -542,7 +542,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C3" s="4">
         <v>80</v>
@@ -557,7 +557,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C4" s="4">
         <v>65</v>
@@ -572,7 +572,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C5" s="4">
         <v>90</v>
@@ -587,7 +587,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C6" s="4">
         <v>72</v>
@@ -602,7 +602,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C7" s="4">
         <v>88</v>
@@ -617,7 +617,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C8" s="4">
         <v>55</v>
@@ -632,7 +632,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C9" s="4">
         <v>78</v>
@@ -647,7 +647,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C10" s="4">
         <v>60</v>
@@ -662,7 +662,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C11" s="4">
         <v>95</v>
@@ -677,7 +677,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C12" s="4">
         <v>70</v>
@@ -689,7 +689,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B14" s="3" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C14" s="1">
         <f>COUNTIF(D3:D12,"LULUS")</f>
@@ -698,7 +698,7 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B15" s="3" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C15" s="1">
         <f>COUNTIF(D3:D12,"TIDAK LULUS")</f>
